--- a/public/ejemplo-strings.xlsx
+++ b/public/ejemplo-strings.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:C51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,9 +412,6 @@
         <v>TRACKER</v>
       </c>
       <c r="C3" t="str">
-        <v>FILA</v>
-      </c>
-      <c r="D3" t="str">
         <v>DC BOX No.</v>
       </c>
     </row>
@@ -423,12 +420,9 @@
         <v>S-5.1.1.1</v>
       </c>
       <c r="B4" t="str">
-        <v>05-001</v>
+        <v>05-001-R1</v>
       </c>
       <c r="C4" t="str">
-        <v>R1</v>
-      </c>
-      <c r="D4" t="str">
         <v>DCB-5.1.1</v>
       </c>
     </row>
@@ -437,10 +431,7 @@
         <v>S-5.1.1.2</v>
       </c>
       <c r="B5" t="str">
-        <v>05-001</v>
-      </c>
-      <c r="C5" t="str">
-        <v>R1</v>
+        <v>05-001-R1</v>
       </c>
     </row>
     <row r="6">
@@ -448,10 +439,7 @@
         <v>S-5.1.1.3</v>
       </c>
       <c r="B6" t="str">
-        <v>05-002</v>
-      </c>
-      <c r="C6" t="str">
-        <v>R1</v>
+        <v>05-002-R1</v>
       </c>
     </row>
     <row r="7">
@@ -459,10 +447,7 @@
         <v>S-5.1.1.4</v>
       </c>
       <c r="B7" t="str">
-        <v>05-002</v>
-      </c>
-      <c r="C7" t="str">
-        <v>R1</v>
+        <v>05-002-R1</v>
       </c>
     </row>
     <row r="8">
@@ -470,10 +455,7 @@
         <v>S-5.1.1.5</v>
       </c>
       <c r="B8" t="str">
-        <v>05-003</v>
-      </c>
-      <c r="C8" t="str">
-        <v>R1</v>
+        <v>05-003-R1</v>
       </c>
     </row>
     <row r="9">
@@ -481,10 +463,7 @@
         <v>S-5.1.1.6</v>
       </c>
       <c r="B9" t="str">
-        <v>05-003</v>
-      </c>
-      <c r="C9" t="str">
-        <v>R1</v>
+        <v>05-003-R1</v>
       </c>
     </row>
     <row r="10">
@@ -492,10 +471,7 @@
         <v>S-5.1.1.7</v>
       </c>
       <c r="B10" t="str">
-        <v>05-004</v>
-      </c>
-      <c r="C10" t="str">
-        <v>R1</v>
+        <v>05-004-R1</v>
       </c>
     </row>
     <row r="11">
@@ -503,10 +479,7 @@
         <v>S-5.1.1.8</v>
       </c>
       <c r="B11" t="str">
-        <v>05-004</v>
-      </c>
-      <c r="C11" t="str">
-        <v>R1</v>
+        <v>05-004-R1</v>
       </c>
     </row>
     <row r="12">
@@ -514,12 +487,9 @@
         <v>S-5.1.2.1</v>
       </c>
       <c r="B12" t="str">
-        <v>05-005</v>
+        <v>05-005-R1</v>
       </c>
       <c r="C12" t="str">
-        <v>R1</v>
-      </c>
-      <c r="D12" t="str">
         <v>DCB-5.1.2</v>
       </c>
     </row>
@@ -528,10 +498,7 @@
         <v>S-5.1.2.2</v>
       </c>
       <c r="B13" t="str">
-        <v>05-005</v>
-      </c>
-      <c r="C13" t="str">
-        <v>R1</v>
+        <v>05-005-R1</v>
       </c>
     </row>
     <row r="14">
@@ -539,10 +506,7 @@
         <v>S-5.1.2.3</v>
       </c>
       <c r="B14" t="str">
-        <v>05-006</v>
-      </c>
-      <c r="C14" t="str">
-        <v>R1</v>
+        <v>05-006-R1</v>
       </c>
     </row>
     <row r="15">
@@ -550,10 +514,7 @@
         <v>S-5.1.2.4</v>
       </c>
       <c r="B15" t="str">
-        <v>05-006</v>
-      </c>
-      <c r="C15" t="str">
-        <v>R1</v>
+        <v>05-006-R1</v>
       </c>
     </row>
     <row r="16">
@@ -561,10 +522,7 @@
         <v>S-5.1.2.5</v>
       </c>
       <c r="B16" t="str">
-        <v>05-007</v>
-      </c>
-      <c r="C16" t="str">
-        <v>R1</v>
+        <v>05-007-R1</v>
       </c>
     </row>
     <row r="17">
@@ -572,10 +530,7 @@
         <v>S-5.1.2.6</v>
       </c>
       <c r="B17" t="str">
-        <v>05-007</v>
-      </c>
-      <c r="C17" t="str">
-        <v>R1</v>
+        <v>05-007-R1</v>
       </c>
     </row>
     <row r="18">
@@ -583,10 +538,7 @@
         <v>S-5.1.2.7</v>
       </c>
       <c r="B18" t="str">
-        <v>05-008</v>
-      </c>
-      <c r="C18" t="str">
-        <v>R1</v>
+        <v>05-008-R1</v>
       </c>
     </row>
     <row r="19">
@@ -594,10 +546,7 @@
         <v>S-5.1.2.8</v>
       </c>
       <c r="B19" t="str">
-        <v>05-008</v>
-      </c>
-      <c r="C19" t="str">
-        <v>R1</v>
+        <v>05-008-R1</v>
       </c>
     </row>
     <row r="20">
@@ -605,12 +554,9 @@
         <v>S-5.1.3.1</v>
       </c>
       <c r="B20" t="str">
-        <v>05-009</v>
+        <v>05-009-R1</v>
       </c>
       <c r="C20" t="str">
-        <v>R1</v>
-      </c>
-      <c r="D20" t="str">
         <v>DCB-5.1.3</v>
       </c>
     </row>
@@ -619,10 +565,7 @@
         <v>S-5.1.3.2</v>
       </c>
       <c r="B21" t="str">
-        <v>05-009</v>
-      </c>
-      <c r="C21" t="str">
-        <v>R1</v>
+        <v>05-009-R1</v>
       </c>
     </row>
     <row r="22">
@@ -630,10 +573,7 @@
         <v>S-5.1.3.3</v>
       </c>
       <c r="B22" t="str">
-        <v>05-010</v>
-      </c>
-      <c r="C22" t="str">
-        <v>R1</v>
+        <v>05-010-R1</v>
       </c>
     </row>
     <row r="23">
@@ -641,10 +581,7 @@
         <v>S-5.1.3.4</v>
       </c>
       <c r="B23" t="str">
-        <v>05-010</v>
-      </c>
-      <c r="C23" t="str">
-        <v>R1</v>
+        <v>05-010-R1</v>
       </c>
     </row>
     <row r="24">
@@ -652,10 +589,7 @@
         <v>S-5.1.3.5</v>
       </c>
       <c r="B24" t="str">
-        <v>05-011</v>
-      </c>
-      <c r="C24" t="str">
-        <v>R1</v>
+        <v>05-011-R1</v>
       </c>
     </row>
     <row r="25">
@@ -663,10 +597,7 @@
         <v>S-5.1.3.6</v>
       </c>
       <c r="B25" t="str">
-        <v>05-011</v>
-      </c>
-      <c r="C25" t="str">
-        <v>R1</v>
+        <v>05-011-R1</v>
       </c>
     </row>
     <row r="26">
@@ -674,10 +605,7 @@
         <v>S-5.1.3.7</v>
       </c>
       <c r="B26" t="str">
-        <v>05-012</v>
-      </c>
-      <c r="C26" t="str">
-        <v>R1</v>
+        <v>05-012-R1</v>
       </c>
     </row>
     <row r="27">
@@ -685,10 +613,7 @@
         <v>S-5.1.3.8</v>
       </c>
       <c r="B27" t="str">
-        <v>05-012</v>
-      </c>
-      <c r="C27" t="str">
-        <v>R1</v>
+        <v>05-012-R1</v>
       </c>
     </row>
     <row r="28">
@@ -696,12 +621,9 @@
         <v>S-5.1.4.1</v>
       </c>
       <c r="B28" t="str">
-        <v>05-013</v>
+        <v>05-013-R1</v>
       </c>
       <c r="C28" t="str">
-        <v>R1</v>
-      </c>
-      <c r="D28" t="str">
         <v>DCB-5.1.4</v>
       </c>
     </row>
@@ -710,10 +632,7 @@
         <v>S-5.1.4.2</v>
       </c>
       <c r="B29" t="str">
-        <v>05-013</v>
-      </c>
-      <c r="C29" t="str">
-        <v>R1</v>
+        <v>05-013-R1</v>
       </c>
     </row>
     <row r="30">
@@ -721,10 +640,7 @@
         <v>S-5.1.4.3</v>
       </c>
       <c r="B30" t="str">
-        <v>05-014</v>
-      </c>
-      <c r="C30" t="str">
-        <v>R1</v>
+        <v>05-014-R1</v>
       </c>
     </row>
     <row r="31">
@@ -732,10 +648,7 @@
         <v>S-5.1.4.4</v>
       </c>
       <c r="B31" t="str">
-        <v>05-014</v>
-      </c>
-      <c r="C31" t="str">
-        <v>R1</v>
+        <v>05-014-R1</v>
       </c>
     </row>
     <row r="32">
@@ -743,10 +656,7 @@
         <v>S-5.1.4.5</v>
       </c>
       <c r="B32" t="str">
-        <v>05-015</v>
-      </c>
-      <c r="C32" t="str">
-        <v>R1</v>
+        <v>05-015-R1</v>
       </c>
     </row>
     <row r="33">
@@ -754,10 +664,7 @@
         <v>S-5.1.4.6</v>
       </c>
       <c r="B33" t="str">
-        <v>05-015</v>
-      </c>
-      <c r="C33" t="str">
-        <v>R1</v>
+        <v>05-015-R1</v>
       </c>
     </row>
     <row r="34">
@@ -765,10 +672,7 @@
         <v>S-5.1.4.7</v>
       </c>
       <c r="B34" t="str">
-        <v>05-016</v>
-      </c>
-      <c r="C34" t="str">
-        <v>R1</v>
+        <v>05-016-R1</v>
       </c>
     </row>
     <row r="35">
@@ -776,10 +680,7 @@
         <v>S-5.1.4.8</v>
       </c>
       <c r="B35" t="str">
-        <v>05-016</v>
-      </c>
-      <c r="C35" t="str">
-        <v>R1</v>
+        <v>05-016-R1</v>
       </c>
     </row>
     <row r="36">
@@ -787,12 +688,9 @@
         <v>S-5.1.5.1</v>
       </c>
       <c r="B36" t="str">
-        <v>05-017</v>
+        <v>05-017-R1</v>
       </c>
       <c r="C36" t="str">
-        <v>R1</v>
-      </c>
-      <c r="D36" t="str">
         <v>DCB-5.1.5</v>
       </c>
     </row>
@@ -801,10 +699,7 @@
         <v>S-5.1.5.2</v>
       </c>
       <c r="B37" t="str">
-        <v>05-017</v>
-      </c>
-      <c r="C37" t="str">
-        <v>R1</v>
+        <v>05-017-R1</v>
       </c>
     </row>
     <row r="38">
@@ -812,10 +707,7 @@
         <v>S-5.1.5.3</v>
       </c>
       <c r="B38" t="str">
-        <v>05-018</v>
-      </c>
-      <c r="C38" t="str">
-        <v>R1</v>
+        <v>05-018-R1</v>
       </c>
     </row>
     <row r="39">
@@ -823,10 +715,7 @@
         <v>S-5.1.5.4</v>
       </c>
       <c r="B39" t="str">
-        <v>05-018</v>
-      </c>
-      <c r="C39" t="str">
-        <v>R1</v>
+        <v>05-018-R1</v>
       </c>
     </row>
     <row r="40">
@@ -834,10 +723,7 @@
         <v>S-5.1.5.5</v>
       </c>
       <c r="B40" t="str">
-        <v>05-019</v>
-      </c>
-      <c r="C40" t="str">
-        <v>R1</v>
+        <v>05-019-R1</v>
       </c>
     </row>
     <row r="41">
@@ -845,10 +731,7 @@
         <v>S-5.1.5.6</v>
       </c>
       <c r="B41" t="str">
-        <v>05-019</v>
-      </c>
-      <c r="C41" t="str">
-        <v>R1</v>
+        <v>05-019-R1</v>
       </c>
     </row>
     <row r="42">
@@ -856,10 +739,7 @@
         <v>S-5.1.5.7</v>
       </c>
       <c r="B42" t="str">
-        <v>05-020</v>
-      </c>
-      <c r="C42" t="str">
-        <v>R1</v>
+        <v>05-020-R1</v>
       </c>
     </row>
     <row r="43">
@@ -867,10 +747,7 @@
         <v>S-5.1.5.8</v>
       </c>
       <c r="B43" t="str">
-        <v>05-020</v>
-      </c>
-      <c r="C43" t="str">
-        <v>R1</v>
+        <v>05-020-R1</v>
       </c>
     </row>
     <row r="44">
@@ -878,12 +755,9 @@
         <v>S-5.1.6.1</v>
       </c>
       <c r="B44" t="str">
-        <v>05-021</v>
+        <v>05-021-R1</v>
       </c>
       <c r="C44" t="str">
-        <v>R1</v>
-      </c>
-      <c r="D44" t="str">
         <v>DCB-5.1.6</v>
       </c>
     </row>
@@ -892,10 +766,7 @@
         <v>S-5.1.6.2</v>
       </c>
       <c r="B45" t="str">
-        <v>05-021</v>
-      </c>
-      <c r="C45" t="str">
-        <v>R1</v>
+        <v>05-021-R1</v>
       </c>
     </row>
     <row r="46">
@@ -903,10 +774,7 @@
         <v>S-5.1.6.3</v>
       </c>
       <c r="B46" t="str">
-        <v>05-022</v>
-      </c>
-      <c r="C46" t="str">
-        <v>R1</v>
+        <v>05-022-R1</v>
       </c>
     </row>
     <row r="47">
@@ -914,10 +782,7 @@
         <v>S-5.1.6.4</v>
       </c>
       <c r="B47" t="str">
-        <v>05-022</v>
-      </c>
-      <c r="C47" t="str">
-        <v>R1</v>
+        <v>05-022-R1</v>
       </c>
     </row>
     <row r="48">
@@ -925,10 +790,7 @@
         <v>S-5.1.6.5</v>
       </c>
       <c r="B48" t="str">
-        <v>05-023</v>
-      </c>
-      <c r="C48" t="str">
-        <v>R1</v>
+        <v>05-023-R1</v>
       </c>
     </row>
     <row r="49">
@@ -936,10 +798,7 @@
         <v>S-5.1.6.6</v>
       </c>
       <c r="B49" t="str">
-        <v>05-023</v>
-      </c>
-      <c r="C49" t="str">
-        <v>R1</v>
+        <v>05-023-R1</v>
       </c>
     </row>
     <row r="50">
@@ -947,10 +806,7 @@
         <v>S-5.1.6.7</v>
       </c>
       <c r="B50" t="str">
-        <v>05-024</v>
-      </c>
-      <c r="C50" t="str">
-        <v>R1</v>
+        <v>05-024-R1</v>
       </c>
     </row>
     <row r="51">
@@ -958,15 +814,12 @@
         <v>S-5.1.6.8</v>
       </c>
       <c r="B51" t="str">
-        <v>05-024</v>
-      </c>
-      <c r="C51" t="str">
-        <v>R1</v>
+        <v>05-024-R1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
   </ignoredErrors>
 </worksheet>
 </file>